--- a/frontend/Modele_Import_Risque_Marche.xlsx
+++ b/frontend/Modele_Import_Risque_Marche.xlsx
@@ -9,8 +9,6 @@
   <sheets>
     <sheet name="Obligations" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Actions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Historique Prix Obligations" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Historique Cours Actions" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +465,16 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Prix de marché (%)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>Prix d'émission</t>
         </is>
       </c>
@@ -509,7 +517,7 @@
       <c r="I2" t="n">
         <v>5000</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>100</v>
       </c>
     </row>
@@ -524,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,132 +543,25 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Type d'instrument</t>
+          <t>Émetteur / Société</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Émetteur / Société</t>
+          <t>Secteur</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Secteur</t>
+          <t>Quantité</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Pays / marché</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
-        <is>
-          <t>Bourse</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Devise</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Intention comptable</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Quantité</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Prix d'acquisition</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Cours actuel</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Bêta</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Volatilité annualisée (%)</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Rendement dividende (%)</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Liquide et diversifié (Oui/Non)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ID Titre</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Prix de marché</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ID Instrument</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
         <is>
           <t>Cours de clôture</t>
         </is>
